--- a/Config/ItemConfig.xlsx
+++ b/Config/ItemConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -70,6 +70,26 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -77,7 +97,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,6 +108,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -114,11 +142,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -181,7 +212,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -216,7 +247,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -425,74 +456,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="45.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="45.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.75" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Config/ItemConfig.xlsx
+++ b/Config/ItemConfig.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="15840"/>
+    <workbookView windowWidth="12645" windowHeight="9090"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -40,64 +40,77 @@
     <t>Id</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>NumOfUsesPerRound</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>技能图标</t>
+  </si>
+  <si>
+    <t>每回合可使用次数</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
-    <t>1010001</t>
-  </si>
-  <si>
-    <t>卡德大陆的常用货币,可以用来购买日常所需材料</t>
-  </si>
-  <si>
-    <t>1010002</t>
-  </si>
-  <si>
-    <t>珍贵而又精美的钻石,可以用来购买日常所需材料</t>
-  </si>
-  <si>
-    <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Currency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>101</t>
+  </si>
+  <si>
+    <t>搓牌</t>
+  </si>
+  <si>
+    <t>使用后,对自身一张牌进行随机替换,花色与牌点都会随机替换</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>透视</t>
+  </si>
+  <si>
+    <t>使用后,在任意时间,长按一位（包括自己）的手牌进行查看</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>替换</t>
+  </si>
+  <si>
+    <t>使用后,在任意时间,将自己手上的牌丢弃,并重新获得3张牌</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,29 +119,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -136,9 +465,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -149,21 +720,65 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -212,7 +827,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -247,7 +862,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -450,95 +1065,137 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="45.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.75" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="4.45" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="4" max="4" width="8.475" customWidth="1"/>
+    <col min="5" max="5" width="17.9333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="45.375" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" customFormat="1" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" customFormat="1" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/ItemConfig.xlsx
+++ b/Config/ItemConfig.xlsx
@@ -1,271 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12645" windowHeight="9090"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="12645" windowHeight="9090" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>NumOfUsesPerRound</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>技能图标</t>
-  </si>
-  <si>
-    <t>每回合可使用次数</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>搓牌</t>
-  </si>
-  <si>
-    <t>使用后,对自身一张牌进行随机替换,花色与牌点都会随机替换</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>透视</t>
-  </si>
-  <si>
-    <t>使用后,在任意时间,长按一位（包括自己）的手牌进行查看</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>替换</t>
-  </si>
-  <si>
-    <t>使用后,在任意时间,将自己手上的牌丢弃,并重新获得3张牌</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -565,164 +471,165 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -776,11 +683,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1069,133 +1039,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="4.45" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="4" width="8.475" customWidth="1"/>
-    <col min="5" max="5" width="17.9333333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="45.375" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col width="9" customWidth="1" style="1" min="1" max="1"/>
+    <col width="4.45" customWidth="1" style="1" min="2" max="2"/>
+    <col width="7.5" customWidth="1" style="3" min="3" max="3"/>
+    <col width="8.475" customWidth="1" style="3" min="4" max="4"/>
+    <col width="17.9333333333333" customWidth="1" style="2" min="5" max="5"/>
+    <col width="45.375" customWidth="1" style="3" min="6" max="6"/>
+    <col width="11.875" customWidth="1" style="1" min="7" max="7"/>
+    <col width="34.75" customWidth="1" style="1" min="8" max="8"/>
+    <col width="9" customWidth="1" style="1" min="9" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>NumOfUsesPerRound</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>技能图标</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>每回合可使用次数</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" s="3">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>搓牌</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>使用后,对自身一张牌进行随机替换,花色与牌点都会随机替换</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+    </row>
+    <row r="6" s="3">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>透视</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>使用后,在任意时间,长按一位（包括自己）的手牌进行查看</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>替换</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:8">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2">
-        <v>3</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:8">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>使用后,在任意时间,将自己手上的牌丢弃,并重新获得5张牌</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>